--- a/EC2_Performance_Analysis_Batch_Dump.xlsx
+++ b/EC2_Performance_Analysis_Batch_Dump.xlsx
@@ -33,19 +33,19 @@
       <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
       <i val="1"/>
       <color rgb="00CCCCCC"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="00262626"/>
-      <sz val="12"/>
+      <color rgb="001F1F1F"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -62,7 +62,7 @@
       <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="8">
@@ -92,8 +92,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9F9F9"/>
-        <bgColor rgb="00F9F9F9"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,8 +104,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -589,7 +589,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【インフラ診断・評価報告書】契約管理アプリ テーブルダンプ時におけるCPU高負荷事象の分析と対策提言</t>
+          <t>【インフラ性能診断報告書】契約管理アプリ テーブルダンプ時におけるCPU高負荷事象の分析と対策提言</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>発行日: 2026年10月 | 診断対象: IT環境バッチサーバ (8 vCPU / 16 GiB) / 本番環境予定 (32 vCPU) | 分類: インフラ性能評価・アーキテクチャ設計</t>
+          <t>発行日: 2026年10月 | 診断対象: IT環境バッチ (c7a.2xlarge: 8 vCPU / 16 GiB / Up to 12.5Gbps) / 本番環境 (c7a.8xlarge: 32 vCPU / 64 GiB) | 分類: インフラ性能評価・アーキテクチャ設計</t>
         </is>
       </c>
     </row>
@@ -617,8 +617,8 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>【一般的な正常事象】
-Linuxのtopコマンド（Irixモード）は1コア=100%として算出するため、マルチスレッド動作するJava JVMプロセスが複数コアを使うと100%を超えるのは完全な正常仕様です。システム全体としてもバッチ処理がCPUを使い切るのは想定動作です。</t>
+          <t>【極めて一般的な正常事象】
+Linuxのtopコマンド（Irixモード）は1コア=100%として積算するため、マルチスレッド動作するJava JVMプロセスが複数コアを消費すると100%（実測125%等）を超えるのは完全な仕様通りの正常動作です。またバッチ処理がCPUを上限まで使い切るのは、ハードウェア資産を最大活用する健全な動作です。</t>
         </is>
       </c>
       <c r="D6" s="5" t="n"/>
@@ -644,8 +644,8 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>【OLTP標準値適用の可能性大】
-一般的にWarning: 70~80%、Critical: 85~90%（5分平均）。バッチ処理とWeb/AP処理を区別せずに同一のしきい値が設定されているため、正常なバッチ高負荷でクリティカルが誤発報しています。</t>
+          <t>【OLTP用しきい値が流用されている可能性大】
+一般的なクラウド標準（Web/AP向け）の Warning: 70~80%、Critical: 85~90%（評価期間5分）が適用されていると推測されます。バッチ処理と常時サービスを同一基準で監視しているため、正常なバッチ高負荷でクリティカルが誤発報しています。</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
@@ -671,8 +671,8 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>【サイジング: 概ね妥当 / 監視域値: 不適切】
-メモリは16GB中5.5GB使用・空き9.8GBと余裕あり。CPU 8vCPUに対して10並列は過密。監視域値はバッチ時間帯の静観設定や判定期間の延長（15分など）に見直すべきです。</t>
+          <t>【サイジング: 妥当 (c7a.2xlarge) / 監視域値: 不適切】
+最新世代のc7a.2xlarge（AMD Genoa, Zen 4, 8vCPU/16GB, Up to 12.5Gbps）は極めて高性能であり、メモリも16GB中5.5GB使用・空き9.8GBと潤沢です。CPU一時飽和は「多重度設定」に起因しており、スペック増強ではなくJP1マルチ数と監視域値の見直しが必須です。</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
@@ -698,8 +698,8 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>【8（または6~7）への削減を強く推奨】
-8vCPUに対して10JVMを動かすと、スレッド競合とコンテキストスイッチ（切替損失）が激増しLoad Avgが17.59まで悪化。並列度を8または7に絞った方が、実はバッチ終了時間は早くなります。</t>
+          <t>【「8」（またはベスト推奨「7」）への変更を強く推奨】
+8vCPUに対して10JVMを動かすと、CPU要求量（約12コア分）が供給量（8コア）を上回り、コンテキストスイッチとCPUキャッシュ破棄が激増してLoad Avgが17.59まで悪化します。並列度を7〜8に絞った方が、実は全体のバッチ完了時間は短縮されます。</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
@@ -719,14 +719,14 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>設問 5: 本番環境 58JVM / 32vCPU / 32マルチ</t>
+          <t>設問 5: 本番 58JVM / 32vCPU / 32マルチ</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>【32マルチは上限ギリギリ、24~28マルチを推奨】
-58ジョブを同時32並列で流す運用は物理コアと1:1ですが、JVM内部スレッド（GC/JIT）が複数動くためCPU飽和・DB負荷・I/O枯渇を招く恐れがあります。安全推奨値は24~28並列です。</t>
+          <t>【32マルチは上限ギリギリ、安全推奨値は「24〜28マルチ」】
+58ジョブを32並列で流す運用は、各JVM内部スレッド（GC/JIT）の重複によりCPUが100%に張り付くほか、最も危険なのは「RDS/Auroraに対する32本同時の大規模SELECTによるDB側の枯渇・遅延」です。安全推奨値は24〜28並列から開始することです。</t>
         </is>
       </c>
       <c r="D14" s="5" t="n"/>
@@ -746,14 +746,14 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>設問 6: クリティカル検知への対策要否</t>
+          <t>設問 6: クリティカル検知への対策方針</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>【想定範囲の一時的高負荷だが、運用対策は必須】
-バッチ特性として高負荷は「想定内」ですが、アラート放置は「狼少年化（重大障害の見落とし）」を招くためNG。①並列度適正化、②GCスレッド抑制、③バッチ窓監視見直しの3段構えで恒久対策を行います。</t>
+          <t>【想定範囲の一時的高負荷だが、運用放置は厳禁】
+計算機科学・バッチ特性としては「想定内」ですが、アラート放置は「狼少年化（真の障害の見落とし）」やOS無応答を招くため対策が不可欠です。「①JP1並列度適正化」「②JVM GCスレッド抑制」「③バッチ時間帯の監視しきい値緩和」の3段構えで恒久対策を行います。</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Linux topの仕様（Irixモード）により、マルチスレッドJVMが1プロセスで100%（1コア分）を超えるのは極めて一般的。バッチ全体でもリソース最大利用は設計通り。</t>
+          <t>Linux topの仕様（Irixモード）により、マルチスレッドJVMが1プロセスで100%（1コア分）を超えるのは極めて一般的。バッチ全体でもリソース最大利用は設計通りの健全な動作。</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>動作原理を関係者へ周知。Solarisモード表示またはCloudWatch（100%満点）での評価基準を統一する。</t>
+          <t>動作原理を関係者へ周知。Solarisモード表示またはCloudWatch（100%満点スケール）での評価基準を統一する。</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>推測：CloudWatch CPUUtilization Warning: 80% / Critical: 90%（5分間）。短時間の高負荷で即報知される過敏な設定。</t>
+          <t>推測：CloudWatch CPUUtilization Warning: 80% / Critical: 90%（5分間）。短時間のバッチ高負荷で即報知される過敏な設定。</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>IT環境はc5.2xlarge相当（8vCPU / 16GB）。メモリ使用5.5GB、空き9.8GBと潤沢。CPUのみ一時的飽和状態。</t>
+          <t>IT環境はc7a.2xlarge（8vCPU / 16GB / Up to 12.5Gbps）。メモリ使用5.5GB、空き9.8GBと潤沢。CPUのみ一時的過密状態。</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>JP1マルチ数を「8」または「7」に変更。1コアをOS/管理用に空けることで全体のスループットが最大化。</t>
+          <t>JP1マルチ数を「8」またはベスト推奨「7」に変更。1コアをOS/管理用に空けることで全体のスループットが最大化。</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -1016,12 +1016,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1031,7 +1031,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【実測メトリクス完全解剖】IT環境テーブルダンプ実行時の負荷状況とボトルネック特定</t>
+          <t>【実測メトリクス完全解剖】IT環境 (c7a.2xlarge) テーブルダンプ実行時の負荷状況とボトルネック特定</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 1. 取得メトリクスの項目別詳細解析</t>
+          <t>■ 1. 取得メトリクスの項目別詳細解析（ハードウェア・OS・ランタイム）</t>
         </is>
       </c>
     </row>
@@ -1093,78 +1093,78 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>8vCPUに対して実行待ち・実行中タスクが平均約17.6個存在。急激な上昇（15分前1.99→5分前5.03→1分前17.59）であり、JP1から一斉に10ジョブが起動された瞬間の急峻なキュー滞留を示している。</t>
+          <t>8 vCPUに対して実行待ち・実行中タスクが平均約17.6個存在。急激な上昇（15分前 1.99 → 5分前 5.03 → 1分前 17.59）であり、JP1から一斉に10ジョブが起動された瞬間の急峻なキュー滞留を示している。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>%Cpu(s) us (User)</t>
+          <t>Tasks 内訳</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>843 total (1 run, 841 sleep)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>70.0%以下（通常運用）</t>
+          <t>通常 200〜400 程度</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>高負荷（正常動作）</t>
+          <t>スレッド多数生成</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>CPU時間の96%がJavaアプリケーションのユーザ空間処理（SQLフェッチ、データ型変換、文字列整形、CSV/JSONフォーマット、メモリ展開、GC処理）に正しく使われている。</t>
+          <t>843タスク中841がsleep（I/Oや同期待ち）、1がrunning。Java JVM 10プロセスがそれぞれ数十本のスレッド（GC、ワーカー、DB接続等）をOSネイティブに生成し、大量のLWP（Lightweight Process）が存在。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>%Cpu(s) sy (System)</t>
+          <t>%Cpu(s) us (User)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>15.0%以下</t>
+          <t>70.0%以下（通常運用）</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>極めて健全</t>
+          <t>高負荷（正常動作）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>OSカーネル空間の消費は3.1%と極小。コンテキストスイッチやシステムコール（write/epoll等）によるOS層の過剰なオーバーヘッドはまだ致命的レベルに達していない。</t>
+          <t>CPU時間の96%がJavaアプリケーションのユーザ空間処理（SQLフェッチ、データ型変換、文字列整形、CSV/JSONフォーマット、メモリ展開、GC処理）に正しく使われている。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>%Cpu(s) wa (I/O Wait)</t>
+          <t>%Cpu(s) sy (System)</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>5.0%以下</t>
+          <t>15.0%以下</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1174,245 +1174,394 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>ディスクやEBSへの書き込み待ちによるCPUブロックはほぼゼロ。ダンプデータはLinuxのページキャッシュ（buff/cache: 8.9GB）に非同期に書き込まれているため、I/Oボトルネックではない。</t>
+          <t>OSカーネル空間の消費は3.1%と極小。コンテキストスイッチやシステムコール（write/epoll等）によるOS層の過剰なオーバーヘッドはまだ致命的レベルに達していない。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>%Cpu(s) st (Steal Time)</t>
+          <t>%Cpu(s) wa (I/O Wait)</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>0.0% (完全専用)</t>
+          <t>5.0%以下</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>完璧（健全）</t>
+          <t>極めて健全</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>AWS NitroハイパーバイザーによるCPUスチール（他VMへの割り当て奪取やCPUバースト枯渇）は一切なし。インスタンスへ割り当てられた物理CPU能力が100%提供されている。</t>
+          <t>ディスクやEBSへの書き込み待ちによるCPUブロックはほぼゼロ。ダンプデータはLinuxのページキャッシュ（buff/cache: 8.9GB）に非同期に書き込まれているため、I/Oボトルネックではない。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Memory Used</t>
+          <t>%Cpu(s) hi / si (割り込み)</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>5,557.3 MiB</t>
+          <t>0.1% / 0.0%</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>15,358 MiB (全体)</t>
+          <t>1.0%以下</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>余裕あり (36%)</t>
+          <t>極めて健全</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>実使用メモリは約5.4GB。10JVM起動時でも1JVMあたり約500MB程度の消費に収まっており、メモリ逼迫やOOM（Out of Memory）の懸念は皆無。</t>
+          <t>ハードウェア割り込み（hi）およびソフトウェア割り込み（si）は皆無。c7aの高性能SR-IOVネットワーク（Up to 12.5Gbps）とNitroシステムが安定処理している。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Memory Buff/Cache</t>
+          <t>%Cpu(s) st (Steal Time)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>8,939.6 MiB</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>動的再利用可能</t>
+          <t>0.0% (完全専用)</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>極めて効果的</t>
+          <t>完璧（健全）</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>メモリの約58%（約8.7GB）がOSページキャッシュとして機能。テーブルダンプで生成されたファイルデータが高速にRAMキャッシュされており、ディスクI/O遅延を防いでいる。</t>
+          <t>AWS NitroハイパーバイザーによるCPUスチール（他VMへの割り当て奪取やCPUバースト枯渇）は一切なし。c7aインスタンスへ割り当てられた物理CPU能力が100%専有提供されている。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Swap Used</t>
+          <t>Memory Used</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>0.2 MiB</t>
+          <t>5,557.3 MiB</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>3,814 MiB中 0.2MiB</t>
+          <t>15,358 MiB (全体)</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>完全未使用</t>
+          <t>余裕あり (36%)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>スワップ発生率0.005%。スラッシング（メモリ不足によるディスクスワップ頻発）は全く起きておらず、パフォーマンス低下要因から除外できる。</t>
+          <t>実使用メモリは約5.4GB。10JVM起動時でも1JVMあたり約500MB程度の消費に収まっており、メモリ逼迫やOOM（Out of Memory）の懸念は皆無。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>Memory Buff/Cache</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>8,939.6 MiB</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>動的再利用可能</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>極めて効果的</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>メモリの約58%（約8.7GB）がOSページキャッシュとして機能。テーブルダンプで生成されたファイルデータが高速にRAMキャッシュされており、ディスクI/O遅延を防いでいる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Swap Used</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>0.2 MiB</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>3,814 MiB中 0.2MiB</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>完全未使用</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>スワップ発生率0.005%。スラッシング（メモリ不足によるディスクスワップ頻発）は全く起きておらず、パフォーマンス低下要因から除外できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
           <t>プロセス別 %CPU</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>125.5%, 122.4%, 115.1%...</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>単一コア=100%</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>マルチスレッド動作</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>各JVMプロセスが1.0〜1.3コア分のCPU能力を同時消費。JVM内部でバッチワーカースレッド、G1GC並列スレッド、JITコンパイラがマルチコアで並行稼働している証拠。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>■ 2. topコマンドにおける「%CPU 100%超え」の技術的背景（Irix vs Solarisモード）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>表示モード</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>キー操作</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>100%の定義</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>最大値（8 vCPU環境）</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>最大値（c7a.2xlarge: 8 vCPU）</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>用途・特徴</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>今回の観測結果の解釈</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Irix モード (デフォルト)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Shift + I で切替</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>「1つのCPUコアの100%」</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>800% (8コア × 100%)</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Linux topの標準。プロセス単位の消費量をコア数積算で表示。マルチスレッドアプリの並列度把握に最適。</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>125.5%は「1つのJVMが約1.25コア分の計算資源を同時に消費した」という意味。正常。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>125.5%は「1つのJVMが約1.25コア分の計算資源を同時に消費した」という意味。マルチスレッド動作として完全正常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Solaris モード</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Shift + I で切替</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>「全CPU合計に対する割合」</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>100% (全コア合算を100%と正規化)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>システム全体の総処理能力に対するプロセス占有率を表示。CloudWatchのCPUUtilizationと同じスケール。</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>125.5%をSolarisモードで換算すると、125.5 ÷ 8 = 約 15.7% のマシン全体占有率となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>■ 3. Tasks 843 (1 running, 841 sleeping) のOS内部スケジューリング構造</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>タスク状態</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>実測タスク数</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>OS内部の動作原理</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>バッチ処理における意味と評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>running (実行中)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>CPUコア上でまさにその瞬間に命令を実行しているタスク。コア数（8個）のうち、topコマンド自身またはJVMスレッドがサンプリング瞬間に補足されたもの。</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>topコマンド実行瞬間のスナップショット値。実際には8個のコアがミリ秒単位で交代しながら常時8タスクを実行中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>sleeping (休止・待機)</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>TASK_INTERRUPTIBLE / TASK_UNINTERRUPTIBLE。DBからのソケット受信待ち、ミューテックス待機、GC待機、スリープ待機のスレッド群。</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>10個のJVM内部スレッド（1JVMあたり30〜50スレッド）とOSデーモン。大部分はイベント駆動待機しており、メモリのみ消費しCPUは消費しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>stopped / zombie</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>1 stopped / 0 zombie</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>停止シグナル（SIGSTOP）を受けたプロセスが1件、ゾンビプロセスはゼロ。</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ゾンビプロセス（孤児プロセス）ゼロであり、プロセスのクリーンアップは正常に行われている。</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1453,7 +1602,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 1. 小学生にも1発でわかる！「8口コンロの厨房と10人の料理人」の例え話</t>
+          <t>■ 1. 小学生にも1発でわかる！「最新超火力8口コンロ厨房と10人の二刀流料理人」の例え話</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1626,17 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>サーバ (EC2)</t>
+          <t>最新サーバ (c7a.2xlarge)</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>レストランの大厨房</t>
+          <t>ピカピカの最高級レストラン厨房</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>お料理（契約データの出力）を作る仕事場です。</t>
+          <t>最新型の超高速調理器具（AMD Zen 4）を備えた超強力な仕事場です。</t>
         </is>
       </c>
       <c r="D6" s="15" t="n"/>
@@ -1498,17 +1647,17 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>8 vCPU</t>
+          <t>8 vCPU (仮想コア)</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>8口のガスコンロ（調理台）</t>
+          <t>8口の最新IHコンロ（調理台）</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>同時に使えるコンロは8個しかありません。9個以上は置けません。</t>
+          <t>同時にフライパンを火にかけられる場所は、世界中どこを探しても「8個」しかありません。</t>
         </is>
       </c>
       <c r="D7" s="17" t="n"/>
@@ -1519,17 +1668,17 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>10 JVM (Javaバッチ)</t>
+          <t>Up to 12.5Gbps ネットワーク</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>10人の料理人</t>
+          <t>超特急の食材配達レーン</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>JP1という店長から「今すぐ全員で10品作れ！」と命令されて一斉に厨房に入ってきた状態。</t>
+          <t>倉庫（DB）から契約データの食材が超ハイスピードで途切れず届くため、料理人は食材待ちになりません。</t>
         </is>
       </c>
       <c r="D8" s="15" t="n"/>
@@ -1540,17 +1689,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>CPU 125%消費</t>
+          <t>10 JVM (Javaバッチ)</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>二刀流でフライパンを振る料理人</t>
+          <t>10人のプロ料理人</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>1人の料理人が両手を使って、コンロを1.25個分同時に使って猛スピードで炒め物をしています。</t>
+          <t>JP1という店長から「今すぐ全員で10種類の契約データ炒めを作れ！」と命令されて厨房に殺到しました。</t>
         </is>
       </c>
       <c r="D9" s="17" t="n"/>
@@ -1561,17 +1710,17 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Load Average 17.59</t>
+          <t>CPU 125%消費</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>コンロ待ちの行列（18人）</t>
+          <t>二刀流でフライパンを振る料理人</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>コンロが8個しかないのに、10人の二刀流料理人（12.5口分）が押し寄せ、さらに店長や片付け係も順番待ちしています。</t>
+          <t>1人の料理人が両手を使って、コンロを1.25個分同時に使って猛スピードで炒め物をしています（マルチスレッド）。</t>
         </is>
       </c>
       <c r="D10" s="15" t="n"/>
@@ -1582,17 +1731,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>コンテキストスイッチ</t>
+          <t>Load Average 17.59</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>「ちょっとそこどいて！」の押し問答</t>
+          <t>コンロ待ちの大行列（18人）</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>コンロの取り合いになり、フライパンを置いたり持ち上げたり場所を譲り合う無駄な時間（ロス）ばかりが増えています。</t>
+          <t>コンロが8個しかないのに、10人の二刀流料理人（12.5口分）が押し寄せ、後ろに行列ができて大混雑しています。</t>
         </is>
       </c>
       <c r="D11" s="17" t="n"/>
@@ -1603,17 +1752,17 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>解決策: 並列度を8(7)にする</t>
+          <t>コンテキストスイッチ</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>コンロの数に合わせて順番に調理</t>
+          <t>「ちょっとそこどいて！」の押し問答</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>料理人を7人にして、1口は店長や皿洗い用に空けておきます。押し問答ゼロになり、実はこの方が全員早く帰れます！</t>
+          <t>コンロの取り合いになり、フライパンを置いたり持ち上げたり場所を譲り合う無駄な時間（ロス）ばかりが増えています。</t>
         </is>
       </c>
       <c r="D12" s="15" t="n"/>
@@ -1621,302 +1770,347 @@
       <c r="F12" s="15" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>解決策: 並列度を8(7)にする</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>コンロの数に合わせて順番に調理</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>料理人を7人に減らし、1口は店長や皿洗い用に空けます。押し問答ゼロになり、実はこの方が全員早く帰れます！</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>■ 2. なぜこの仕組みになったのか？ ITアーキテクチャ登場の歴史と背景</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>時代・年代</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>歴史的背景と直面した壁</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>誕生した技術イノベーション</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>現代（本件）への影響と教訓</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>1960~80年代
 メインフレーム時代</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>計算機が超高価だった時代。昼間は窓口業務、夜間は計算機が空くため、翌朝までに一括で大量データを処理する必要があった。</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>【バッチ処理とジョブ管理の誕生】
-CPUを100%限界まで使い切って最短時間で処理を終わらせる設計思想が確立された。JP1やcronの原型。</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>バッチ処理中にCPUが100%近くに達するのは「機械の性能を無駄なく使い切っている」証であり、本来正常な設計思想。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>計算機が国家予算並みに超高価だった時代。昼間は窓口業務、夜間は計算機が空くため、翌朝までに一括で大量データを処理する必要があった。</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>【バッチ処理とジョブ管理の哲学】
+「高価なCPUを遊ばせるな」という思想から、CPUを100%限界まで使い切って最短時間で処理を終わらせる設計思想が確立された。</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>バッチ処理中にCPUが100%近くに達するのは「ハードウェア資産を限界まで使い切っている」証拠であり、本来正常で優秀な設計。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2000年代初頭
 クロック周波数の壁</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Pentium 4時代にCPUの動作周波数が4GHzに達した際、熱暴走と消費電力の限界（物理の壁）に衝突した。</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Pentium 4時代にCPUの動作周波数が4GHzに達した際、熱暴走と消費電力の急増（物理の壁）に衝突し、単一コアの高速化が限界を迎えた。</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>【マルチコア・SMP（対称型マルチプロセッサ）】
-1つのCPUを速くするのを諦め、1つのチップに複数の「コア（脳）」を載せて並列処理する道を選んだ。</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>現在の8 vCPUや32 vCPUの前提。並列度を上げないとCPU能力を引き出せないが、並列にしすぎると管理オーバーヘッドが発生する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+1つのCPUを速くするのを諦め、1つのチップに複数の「コア（脳）」を載せて並列処理する道へと人類は舵を切った。</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>現在の8 vCPUや32 vCPUの前提。並列度を上げないとCPU能力を引き出せないが、コア数以上に並列化すると管理ロスが発生する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Javaスレッドの進化
 (1995~2020年代)</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>初期Java（Green Threads）はOSスレッドを使わずJVM内で疑似並行実行していたがマルチコアを生かせなかった。</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>初期Java（Green Threads）はOSスレッドを使わずJVM内で疑似並行実行していたため、CPUが何コアあっても1コアしか使えなかった。</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>【ネイティブスレッド (1:1モデル)】
 Javaスレッド1本をOSのpthread 1本に直結。これによりJVMが複数コアを同時に消費し「125%」が出せるようになった。</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>1つのJavaバッチが内部で複数スレッド（GC/JIT/ワーカー）を動かすため、JVM数＝CPU使用数ではなく「JVM数 × スレッド係数」となる。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>クラウド仮想化
 (XenからAWS Nitro)</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>従来の仮想マシンはCPU割り当て時にハイパーバイザーの介入遅延やCPU横取り（Steal Time）が発生した。</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>【AWS Nitro System (ハードウェアオフロード)】
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>従来の仮想マシン（Xen等）はCPU割り当て時にハイパーバイザーの介入遅延やCPU横取り（Steal Time）が発生した。</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>【AWS Nitro System (第5世代 / c7a)】
 vCPUは物理コアのハイパースレッディング（HT）として100%専有保証され、Steal Time 0.0%を実現。</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>今回の計測でSteal Time 0.0%が実証。インフラの外部要因ではなく、純粋にゲストOS内のプロセス配置バランスの問題と特定できる。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>ジョブ運用の進化
+(JP1/AJSの役割)</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>数百本ものバッチジョブを無制限に一斉実行すると、CPUもメモリも瞬時にパンクしシステム全体がクラッシュする問題が発生。</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>【ジョブ実行多重度（キュー制御）】
+マシンの物理コア数に合わせて「同時に走らせるジョブの数」を厳密に絞り込み、順次実行するキューイング機構が必須となった。</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>本件の根本解決策。物理コア数（8 vCPU）に対してJP1の多重度を適切に絞る（7〜8）ことで、システムを最速かつ安全に稼働させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>■ 3. テーブルダンプ処理実行時のデータフローとCPU消費パイプライン</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>主な消費リソース</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>今回の実測値との整合性</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>最適化の着眼点</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>① DBフェッチ</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>JDBC経由でDBから契約テーブルレコードを受信</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ネットワークI/O、ソケットバッファ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ネットワーク待ちは微小（CPU sy 3.1%）</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Fetch Sizeのチューニング（デフォルト10件→1000件等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>② オブジェクト展開</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>受信バイナリをJava Entityオブジェクトへデシリアライズ</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>メモリヒープ割当、CPU (us)</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>JVMヒープに一時格納（used 5.5GBと安定）</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>短命オブジェクトの過剰生成抑制</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>③ 文字列整形・変換</t>
+          <t>① DBフェッチ</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>契約データをCSV/TSV/JSON等のダンプ形式へ文字コード変換</t>
+          <t>JDBC経由でDBから契約テーブルレコードを受信</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>CPU (us 95.9%) ← 最大ボトルネック</t>
+          <t>ネットワークI/O (Up to 12.5Gbps)</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>%CPU 125%の正体。文字列連結・文字コード変換の計算負荷</t>
+          <t>ネットワーク帯域が広大で待たされない（CPU sy 3.1%）</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>StringBuilder利用、効率的なCSVシリアライザの採用</t>
+          <t>Fetch Sizeのチューニング（デフォルト10件→1000件等）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>④ ガベージコレクション</t>
+          <t>② オブジェクト展開</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>出力完了した旧世代オブジェクトのメモリ回収 (G1GC/Parallel)</t>
+          <t>受信バイナリをJava Entityオブジェクトへデシリアライズ</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>CPU (us / 並列スレッド)</t>
+          <t>メモリヒープ割当、CPU (us)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>JVMが100%超を消費する要因（バックグラウンドGC稼働）</t>
+          <t>JVMヒープに一時格納（used 5.5GBと安定）</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>-XX:ParallelGCThreads の明示的制限</t>
+          <t>短命オブジェクトの過剰生成抑制</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>③ 文字列整形・変換</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>契約データをCSV/TSV/JSON等のダンプ形式へ文字コード変換</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>CPU (us 95.9%) ← 最大ボトルネック</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>%CPU 125%の正体。文字列連結・文字コード変換の計算負荷</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>StringBuilder利用、効率的なCSVシリアライザの採用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>④ ガベージコレクション</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>出力完了した旧世代オブジェクトのメモリ回収 (G1GC/Parallel)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>CPU (us / 並列スレッド)</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>JVMが100%超を消費する要因（バックグラウンドGC稼働）</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>-XX:ParallelGCThreads の明示的制限</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
           <t>⑤ ディスク出力</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>ファイルへダンプ結果をwriteシステムコールで書き出し</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>OSページキャッシュ (buff/cache)</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>wa 0.8%と極小。8.9GBのbuff/cacheがディスクI/Oを全吸収</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>バッファ付きストリーム（BufferedOutputStream）の適用</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="A1:G2"/>
@@ -1924,6 +2118,7 @@
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
   </mergeCells>
@@ -1952,7 +2147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【徹底比較】IT環境 vs 本番環境における並列度（JP1マルチ数）とCPU・スループット相関検証</t>
+          <t>【徹底比較】IT環境 (c7a.2xlarge) vs 本番環境 (c7a.8xlarge) 並列度とCPU・スループット相関検証</t>
         </is>
       </c>
     </row>
@@ -1960,7 +2155,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 1. IT環境（8 vCPU / 16 GiB）におけるJVM並列数シミュレーション</t>
+          <t>■ 1. IT環境（c7a.2xlarge: 8 vCPU / 16 GiB）におけるJVM並列数シミュレーション</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2229,7 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>非推奨 (CPU飽和・OS遅延・アラート頻発)</t>
+          <t>非推奨 (CPU過密飽和・OS遅延・アラート頻発)</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2347,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ 2. 本番環境（32 vCPU / 58 JVM予定）におけるマルチ数シミュレーションと成立要件</t>
+          <t>■ 2. 本番環境（c7a.8xlarge: 32 vCPU / 64 GiB / 58 JVM予定）におけるマルチ数検証</t>
         </is>
       </c>
     </row>
